--- a/tests/fixtures/2025 Political-Related Sexual Violence Incident Data.xlsx
+++ b/tests/fixtures/2025 Political-Related Sexual Violence Incident Data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="223">
   <si>
     <t>Date</t>
   </si>
@@ -88,129 +88,6 @@
     <t>Date Event Modified</t>
   </si>
   <si>
-    <t>14/09/2025</t>
-  </si>
-  <si>
-    <t>19/08/2025</t>
-  </si>
-  <si>
-    <t>13/08/2025</t>
-  </si>
-  <si>
-    <t>08/08/2025</t>
-  </si>
-  <si>
-    <t>05/08/2025</t>
-  </si>
-  <si>
-    <t>04/08/2025</t>
-  </si>
-  <si>
-    <t>03/08/2025</t>
-  </si>
-  <si>
-    <t>31/07/2025</t>
-  </si>
-  <si>
-    <t>30/07/2025</t>
-  </si>
-  <si>
-    <t>27/07/2025</t>
-  </si>
-  <si>
-    <t>19/07/2025</t>
-  </si>
-  <si>
-    <t>17/07/2025</t>
-  </si>
-  <si>
-    <t>15/07/2025</t>
-  </si>
-  <si>
-    <t>10/07/2025</t>
-  </si>
-  <si>
-    <t>02/07/2025</t>
-  </si>
-  <si>
-    <t>26/06/2025</t>
-  </si>
-  <si>
-    <t>06/06/2025</t>
-  </si>
-  <si>
-    <t>03/06/2025</t>
-  </si>
-  <si>
-    <t>02/06/2025</t>
-  </si>
-  <si>
-    <t>27/05/2025</t>
-  </si>
-  <si>
-    <t>23/05/2025</t>
-  </si>
-  <si>
-    <t>19/05/2025</t>
-  </si>
-  <si>
-    <t>06/05/2025</t>
-  </si>
-  <si>
-    <t>16/04/2025</t>
-  </si>
-  <si>
-    <t>04/04/2025</t>
-  </si>
-  <si>
-    <t>28/03/2025</t>
-  </si>
-  <si>
-    <t>14/03/2025</t>
-  </si>
-  <si>
-    <t>10/03/2025</t>
-  </si>
-  <si>
-    <t>08/03/2025</t>
-  </si>
-  <si>
-    <t>02/03/2025</t>
-  </si>
-  <si>
-    <t>20/02/2025</t>
-  </si>
-  <si>
-    <t>19/02/2025</t>
-  </si>
-  <si>
-    <t>18/02/2025</t>
-  </si>
-  <si>
-    <t>16/02/2025</t>
-  </si>
-  <si>
-    <t>06/02/2025</t>
-  </si>
-  <si>
-    <t>30/01/2025</t>
-  </si>
-  <si>
-    <t>20/01/2025</t>
-  </si>
-  <si>
-    <t>15/01/2025</t>
-  </si>
-  <si>
-    <t>14/01/2025</t>
-  </si>
-  <si>
-    <t>12/01/2025</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>Afghanistan</t>
   </si>
   <si>
@@ -806,81 +683,15 @@
   </si>
   <si>
     <t>89533</t>
-  </si>
-  <si>
-    <t>27/10/2025</t>
-  </si>
-  <si>
-    <t>12/10/2025</t>
-  </si>
-  <si>
-    <t>13/10/2025</t>
-  </si>
-  <si>
-    <t>06/10/2025</t>
-  </si>
-  <si>
-    <t>10/10/2025</t>
-  </si>
-  <si>
-    <t>05/10/2025</t>
-  </si>
-  <si>
-    <t>31/08/2025</t>
-  </si>
-  <si>
-    <t>29/07/2025</t>
-  </si>
-  <si>
-    <t>18/07/2025</t>
-  </si>
-  <si>
-    <t>20/07/2025</t>
-  </si>
-  <si>
-    <t>14/06/2025</t>
-  </si>
-  <si>
-    <t>01/06/2025</t>
-  </si>
-  <si>
-    <t>18/05/2025</t>
-  </si>
-  <si>
-    <t>06/04/2025</t>
-  </si>
-  <si>
-    <t>25/03/2025</t>
-  </si>
-  <si>
-    <t>30/03/2025</t>
-  </si>
-  <si>
-    <t>11/03/2025</t>
-  </si>
-  <si>
-    <t>09/03/2025</t>
-  </si>
-  <si>
-    <t>06/12/2025</t>
-  </si>
-  <si>
-    <t>16/10/2025</t>
-  </si>
-  <si>
-    <t>07/09/2025</t>
-  </si>
-  <si>
-    <t>10/08/2025</t>
-  </si>
-  <si>
-    <t>01/07/2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -910,8 +721,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1284,20 +1096,17 @@
       </c>
     </row>
     <row r="2" spans="1:24">
-      <c r="A2" t="s">
+      <c r="A2" s="1">
+        <v>45914</v>
+      </c>
+      <c r="C2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>65</v>
-      </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="F2">
         <v>36.8</v>
@@ -1306,69 +1115,66 @@
         <v>71.3</v>
       </c>
       <c r="H2" t="s">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="I2" t="s">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="J2" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K2" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="L2" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="M2" t="s">
-        <v>188</v>
+        <v>147</v>
       </c>
       <c r="N2" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O2" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="P2" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q2" t="s">
-        <v>206</v>
+        <v>165</v>
       </c>
       <c r="R2" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S2" t="s">
-        <v>213</v>
+        <v>172</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="V2" t="s">
-        <v>218</v>
-      </c>
-      <c r="W2" t="s">
-        <v>264</v>
-      </c>
-      <c r="X2" t="s">
-        <v>282</v>
+        <v>177</v>
+      </c>
+      <c r="W2" s="1">
+        <v>45957</v>
+      </c>
+      <c r="X2" s="1">
+        <v>45997</v>
       </c>
     </row>
     <row r="3" spans="1:24">
-      <c r="A3" t="s">
+      <c r="A3" s="1">
+        <v>45888</v>
+      </c>
+      <c r="C3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>66</v>
-      </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="F3">
         <v>6</v>
@@ -1377,69 +1183,66 @@
         <v>6.8</v>
       </c>
       <c r="H3" t="s">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="I3" t="s">
-        <v>154</v>
+        <v>113</v>
       </c>
       <c r="J3" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K3" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="L3" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="M3" t="s">
-        <v>189</v>
+        <v>148</v>
       </c>
       <c r="N3" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O3" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="P3" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q3" t="s">
-        <v>207</v>
+        <v>166</v>
       </c>
       <c r="R3" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S3" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>219</v>
-      </c>
-      <c r="W3" t="s">
-        <v>265</v>
-      </c>
-      <c r="X3" t="s">
-        <v>283</v>
+        <v>178</v>
+      </c>
+      <c r="W3" s="1">
+        <v>45942</v>
+      </c>
+      <c r="X3" s="1">
+        <v>45946</v>
       </c>
     </row>
     <row r="4" spans="1:24">
-      <c r="A4" t="s">
+      <c r="A4" s="1">
+        <v>45882</v>
+      </c>
+      <c r="C4" t="s">
         <v>26</v>
       </c>
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" t="s">
-        <v>67</v>
-      </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="F4">
         <v>43.9</v>
@@ -1448,69 +1251,66 @@
         <v>41.1</v>
       </c>
       <c r="H4" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I4" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="J4" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K4" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="L4" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="M4" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="N4" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O4" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="P4" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q4" t="s">
-        <v>208</v>
+        <v>167</v>
       </c>
       <c r="R4" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S4" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="T4">
         <v>1</v>
       </c>
       <c r="V4" t="s">
-        <v>220</v>
-      </c>
-      <c r="W4" t="s">
-        <v>266</v>
-      </c>
-      <c r="X4" t="s">
-        <v>283</v>
+        <v>179</v>
+      </c>
+      <c r="W4" s="1">
+        <v>45943</v>
+      </c>
+      <c r="X4" s="1">
+        <v>45946</v>
       </c>
     </row>
     <row r="5" spans="1:24">
-      <c r="A5" t="s">
+      <c r="A5" s="1">
+        <v>45877</v>
+      </c>
+      <c r="C5" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>68</v>
-      </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="F5">
         <v>-3.3</v>
@@ -1519,69 +1319,66 @@
         <v>120.3</v>
       </c>
       <c r="H5" t="s">
+        <v>109</v>
+      </c>
+      <c r="I5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J5" t="s">
+        <v>121</v>
+      </c>
+      <c r="K5" t="s">
+        <v>126</v>
+      </c>
+      <c r="L5" t="s">
+        <v>146</v>
+      </c>
+      <c r="M5" t="s">
         <v>150</v>
       </c>
-      <c r="I5" t="s">
+      <c r="N5" t="s">
+        <v>155</v>
+      </c>
+      <c r="O5" t="s">
         <v>156</v>
       </c>
-      <c r="J5" t="s">
-        <v>162</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="P5" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q5" t="s">
         <v>167</v>
       </c>
-      <c r="L5" t="s">
-        <v>187</v>
-      </c>
-      <c r="M5" t="s">
-        <v>191</v>
-      </c>
-      <c r="N5" t="s">
-        <v>196</v>
-      </c>
-      <c r="O5" t="s">
-        <v>197</v>
-      </c>
-      <c r="P5" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>208</v>
-      </c>
       <c r="R5" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S5" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="T5">
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>221</v>
-      </c>
-      <c r="W5" t="s">
-        <v>266</v>
-      </c>
-      <c r="X5" t="s">
-        <v>283</v>
+        <v>180</v>
+      </c>
+      <c r="W5" s="1">
+        <v>45943</v>
+      </c>
+      <c r="X5" s="1">
+        <v>45946</v>
       </c>
     </row>
     <row r="6" spans="1:24">
-      <c r="A6" t="s">
+      <c r="A6" s="1">
+        <v>45874</v>
+      </c>
+      <c r="C6" t="s">
         <v>28</v>
       </c>
-      <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" t="s">
-        <v>69</v>
-      </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="F6">
         <v>8.699999999999999</v>
@@ -1590,69 +1387,66 @@
         <v>-83.09999999999999</v>
       </c>
       <c r="H6" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I6" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="J6" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K6" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="L6" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="M6" t="s">
-        <v>189</v>
+        <v>148</v>
       </c>
       <c r="N6" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O6" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="P6" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q6" t="s">
-        <v>208</v>
+        <v>167</v>
       </c>
       <c r="R6" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S6" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="T6">
         <v>1</v>
       </c>
       <c r="V6" t="s">
-        <v>222</v>
-      </c>
-      <c r="W6" t="s">
-        <v>267</v>
-      </c>
-      <c r="X6" t="s">
-        <v>283</v>
+        <v>181</v>
+      </c>
+      <c r="W6" s="1">
+        <v>45936</v>
+      </c>
+      <c r="X6" s="1">
+        <v>45946</v>
       </c>
     </row>
     <row r="7" spans="1:24">
-      <c r="A7" t="s">
+      <c r="A7" s="1">
+        <v>45873</v>
+      </c>
+      <c r="C7" t="s">
         <v>29</v>
       </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" t="s">
-        <v>70</v>
-      </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="F7">
         <v>-2.4</v>
@@ -1661,69 +1455,66 @@
         <v>25.9</v>
       </c>
       <c r="H7" t="s">
-        <v>152</v>
+        <v>111</v>
       </c>
       <c r="I7" t="s">
+        <v>115</v>
+      </c>
+      <c r="J7" t="s">
+        <v>121</v>
+      </c>
+      <c r="K7" t="s">
+        <v>128</v>
+      </c>
+      <c r="L7" t="s">
+        <v>146</v>
+      </c>
+      <c r="M7" t="s">
+        <v>150</v>
+      </c>
+      <c r="N7" t="s">
+        <v>155</v>
+      </c>
+      <c r="O7" t="s">
         <v>156</v>
       </c>
-      <c r="J7" t="s">
-        <v>162</v>
-      </c>
-      <c r="K7" t="s">
-        <v>169</v>
-      </c>
-      <c r="L7" t="s">
-        <v>187</v>
-      </c>
-      <c r="M7" t="s">
-        <v>191</v>
-      </c>
-      <c r="N7" t="s">
-        <v>196</v>
-      </c>
-      <c r="O7" t="s">
-        <v>197</v>
-      </c>
       <c r="P7" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q7" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="R7" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S7" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="T7">
         <v>1</v>
       </c>
       <c r="V7" t="s">
-        <v>223</v>
-      </c>
-      <c r="W7" t="s">
-        <v>268</v>
-      </c>
-      <c r="X7" t="s">
-        <v>283</v>
+        <v>182</v>
+      </c>
+      <c r="W7" s="1">
+        <v>45940</v>
+      </c>
+      <c r="X7" s="1">
+        <v>45946</v>
       </c>
     </row>
     <row r="8" spans="1:24">
-      <c r="A8" t="s">
+      <c r="A8" s="1">
+        <v>45872</v>
+      </c>
+      <c r="C8" t="s">
         <v>30</v>
       </c>
-      <c r="B8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" t="s">
-        <v>71</v>
-      </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="F8">
         <v>-3</v>
@@ -1732,69 +1523,66 @@
         <v>30.1</v>
       </c>
       <c r="H8" t="s">
+        <v>109</v>
+      </c>
+      <c r="I8" t="s">
+        <v>113</v>
+      </c>
+      <c r="J8" t="s">
+        <v>122</v>
+      </c>
+      <c r="K8" t="s">
+        <v>129</v>
+      </c>
+      <c r="L8" t="s">
+        <v>146</v>
+      </c>
+      <c r="M8" t="s">
         <v>150</v>
       </c>
-      <c r="I8" t="s">
-        <v>154</v>
-      </c>
-      <c r="J8" t="s">
-        <v>163</v>
-      </c>
-      <c r="K8" t="s">
-        <v>170</v>
-      </c>
-      <c r="L8" t="s">
-        <v>187</v>
-      </c>
-      <c r="M8" t="s">
-        <v>191</v>
-      </c>
       <c r="N8" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O8" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="P8" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q8" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="R8" t="s">
-        <v>212</v>
+        <v>171</v>
       </c>
       <c r="S8" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="T8">
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>224</v>
-      </c>
-      <c r="W8" t="s">
-        <v>269</v>
-      </c>
-      <c r="X8" t="s">
-        <v>283</v>
+        <v>183</v>
+      </c>
+      <c r="W8" s="1">
+        <v>45935</v>
+      </c>
+      <c r="X8" s="1">
+        <v>45946</v>
       </c>
     </row>
     <row r="9" spans="1:24">
-      <c r="A9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" t="s">
-        <v>64</v>
+      <c r="A9" s="1">
+        <v>45869</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="E9" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="F9">
         <v>-4.4</v>
@@ -1803,69 +1591,66 @@
         <v>15.2</v>
       </c>
       <c r="H9" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I9" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="J9" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K9" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="L9" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="M9" t="s">
-        <v>189</v>
+        <v>148</v>
       </c>
       <c r="N9" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O9" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="P9" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q9" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="R9" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S9" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="T9">
         <v>1</v>
       </c>
       <c r="V9" t="s">
-        <v>225</v>
-      </c>
-      <c r="W9" t="s">
-        <v>268</v>
-      </c>
-      <c r="X9" t="s">
-        <v>283</v>
+        <v>184</v>
+      </c>
+      <c r="W9" s="1">
+        <v>45940</v>
+      </c>
+      <c r="X9" s="1">
+        <v>45946</v>
       </c>
     </row>
     <row r="10" spans="1:24">
-      <c r="A10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" t="s">
-        <v>64</v>
+      <c r="A10" s="1">
+        <v>45868</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="F10">
         <v>30.1</v>
@@ -1874,69 +1659,66 @@
         <v>76.7</v>
       </c>
       <c r="H10" t="s">
+        <v>110</v>
+      </c>
+      <c r="I10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J10" t="s">
+        <v>121</v>
+      </c>
+      <c r="K10" t="s">
+        <v>130</v>
+      </c>
+      <c r="L10" t="s">
+        <v>145</v>
+      </c>
+      <c r="M10" t="s">
         <v>151</v>
       </c>
-      <c r="I10" t="s">
-        <v>155</v>
-      </c>
-      <c r="J10" t="s">
-        <v>162</v>
-      </c>
-      <c r="K10" t="s">
-        <v>171</v>
-      </c>
-      <c r="L10" t="s">
-        <v>186</v>
-      </c>
-      <c r="M10" t="s">
-        <v>192</v>
-      </c>
       <c r="N10" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O10" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="P10" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q10" t="s">
-        <v>208</v>
+        <v>167</v>
       </c>
       <c r="R10" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S10" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="T10">
         <v>1</v>
       </c>
       <c r="V10" t="s">
-        <v>226</v>
-      </c>
-      <c r="W10" t="s">
-        <v>266</v>
-      </c>
-      <c r="X10" t="s">
-        <v>283</v>
+        <v>185</v>
+      </c>
+      <c r="W10" s="1">
+        <v>45943</v>
+      </c>
+      <c r="X10" s="1">
+        <v>45946</v>
       </c>
     </row>
     <row r="11" spans="1:24">
-      <c r="A11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" t="s">
-        <v>64</v>
+      <c r="A11" s="1">
+        <v>45865</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="F11">
         <v>-3.3</v>
@@ -1945,69 +1727,66 @@
         <v>-60.6</v>
       </c>
       <c r="H11" t="s">
-        <v>152</v>
+        <v>111</v>
       </c>
       <c r="I11" t="s">
+        <v>115</v>
+      </c>
+      <c r="J11" t="s">
+        <v>121</v>
+      </c>
+      <c r="K11" t="s">
+        <v>131</v>
+      </c>
+      <c r="L11" t="s">
+        <v>146</v>
+      </c>
+      <c r="M11" t="s">
+        <v>148</v>
+      </c>
+      <c r="N11" t="s">
+        <v>155</v>
+      </c>
+      <c r="O11" t="s">
         <v>156</v>
       </c>
-      <c r="J11" t="s">
-        <v>162</v>
-      </c>
-      <c r="K11" t="s">
-        <v>172</v>
-      </c>
-      <c r="L11" t="s">
-        <v>187</v>
-      </c>
-      <c r="M11" t="s">
-        <v>189</v>
-      </c>
-      <c r="N11" t="s">
-        <v>196</v>
-      </c>
-      <c r="O11" t="s">
-        <v>197</v>
-      </c>
       <c r="P11" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q11" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="R11" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S11" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="T11">
         <v>1</v>
       </c>
       <c r="V11" t="s">
-        <v>227</v>
-      </c>
-      <c r="W11" t="s">
-        <v>269</v>
-      </c>
-      <c r="X11" t="s">
-        <v>283</v>
+        <v>186</v>
+      </c>
+      <c r="W11" s="1">
+        <v>45935</v>
+      </c>
+      <c r="X11" s="1">
+        <v>45946</v>
       </c>
     </row>
     <row r="12" spans="1:24">
-      <c r="A12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" t="s">
-        <v>64</v>
+      <c r="A12" s="1">
+        <v>45857</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="F12">
         <v>29.1</v>
@@ -2016,69 +1795,66 @@
         <v>77.59999999999999</v>
       </c>
       <c r="H12" t="s">
+        <v>109</v>
+      </c>
+      <c r="I12" t="s">
+        <v>117</v>
+      </c>
+      <c r="J12" t="s">
+        <v>121</v>
+      </c>
+      <c r="K12" t="s">
+        <v>130</v>
+      </c>
+      <c r="L12" t="s">
+        <v>145</v>
+      </c>
+      <c r="M12" t="s">
         <v>150</v>
       </c>
-      <c r="I12" t="s">
-        <v>158</v>
-      </c>
-      <c r="J12" t="s">
-        <v>162</v>
-      </c>
-      <c r="K12" t="s">
-        <v>171</v>
-      </c>
-      <c r="L12" t="s">
-        <v>186</v>
-      </c>
-      <c r="M12" t="s">
-        <v>191</v>
-      </c>
       <c r="N12" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O12" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="P12" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q12" t="s">
-        <v>206</v>
+        <v>165</v>
       </c>
       <c r="R12" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S12" t="s">
-        <v>213</v>
+        <v>172</v>
       </c>
       <c r="T12">
         <v>2</v>
       </c>
       <c r="V12" t="s">
-        <v>228</v>
-      </c>
-      <c r="W12" t="s">
-        <v>266</v>
-      </c>
-      <c r="X12" t="s">
-        <v>283</v>
+        <v>187</v>
+      </c>
+      <c r="W12" s="1">
+        <v>45943</v>
+      </c>
+      <c r="X12" s="1">
+        <v>45946</v>
       </c>
     </row>
     <row r="13" spans="1:24">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>64</v>
+      <c r="A13" s="1">
+        <v>45855</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="F13">
         <v>-3.6</v>
@@ -2087,69 +1863,66 @@
         <v>29.3</v>
       </c>
       <c r="H13" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I13" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="J13" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="K13" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="L13" t="s">
-        <v>187</v>
+        <v>146</v>
       </c>
       <c r="M13" t="s">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="N13" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O13" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="P13" t="s">
-        <v>203</v>
+        <v>162</v>
       </c>
       <c r="Q13" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="R13" t="s">
-        <v>212</v>
+        <v>171</v>
       </c>
       <c r="S13" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="T13">
         <v>1</v>
       </c>
       <c r="V13" t="s">
-        <v>229</v>
-      </c>
-      <c r="W13" t="s">
-        <v>269</v>
-      </c>
-      <c r="X13" t="s">
-        <v>283</v>
+        <v>188</v>
+      </c>
+      <c r="W13" s="1">
+        <v>45935</v>
+      </c>
+      <c r="X13" s="1">
+        <v>45946</v>
       </c>
     </row>
     <row r="14" spans="1:24">
-      <c r="A14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" t="s">
-        <v>64</v>
+      <c r="A14" s="1">
+        <v>45853</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="F14">
         <v>24.9</v>
@@ -2158,69 +1931,66 @@
         <v>79.5</v>
       </c>
       <c r="H14" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I14" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="J14" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K14" t="s">
-        <v>171</v>
+        <v>130</v>
       </c>
       <c r="L14" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="M14" t="s">
-        <v>193</v>
+        <v>152</v>
       </c>
       <c r="N14" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O14" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="P14" t="s">
-        <v>204</v>
+        <v>163</v>
       </c>
       <c r="Q14" t="s">
-        <v>208</v>
+        <v>167</v>
       </c>
       <c r="R14" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S14" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="T14">
         <v>4</v>
       </c>
       <c r="V14" t="s">
-        <v>230</v>
-      </c>
-      <c r="W14" t="s">
-        <v>266</v>
-      </c>
-      <c r="X14" t="s">
-        <v>283</v>
+        <v>189</v>
+      </c>
+      <c r="W14" s="1">
+        <v>45943</v>
+      </c>
+      <c r="X14" s="1">
+        <v>45946</v>
       </c>
     </row>
     <row r="15" spans="1:24">
-      <c r="A15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" t="s">
-        <v>64</v>
+      <c r="A15" s="1">
+        <v>45848</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="E15" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="F15">
         <v>-3.2</v>
@@ -2229,69 +1999,66 @@
         <v>29.7</v>
       </c>
       <c r="H15" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I15" t="s">
-        <v>159</v>
+        <v>118</v>
       </c>
       <c r="J15" t="s">
+        <v>121</v>
+      </c>
+      <c r="K15" t="s">
+        <v>132</v>
+      </c>
+      <c r="L15" t="s">
+        <v>146</v>
+      </c>
+      <c r="M15" t="s">
+        <v>150</v>
+      </c>
+      <c r="N15" t="s">
+        <v>155</v>
+      </c>
+      <c r="O15" t="s">
+        <v>156</v>
+      </c>
+      <c r="P15" t="s">
         <v>162</v>
       </c>
-      <c r="K15" t="s">
-        <v>173</v>
-      </c>
-      <c r="L15" t="s">
-        <v>187</v>
-      </c>
-      <c r="M15" t="s">
-        <v>191</v>
-      </c>
-      <c r="N15" t="s">
-        <v>196</v>
-      </c>
-      <c r="O15" t="s">
-        <v>197</v>
-      </c>
-      <c r="P15" t="s">
-        <v>203</v>
-      </c>
       <c r="Q15" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="R15" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S15" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="T15">
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>231</v>
-      </c>
-      <c r="W15" t="s">
-        <v>270</v>
-      </c>
-      <c r="X15" t="s">
-        <v>284</v>
+        <v>190</v>
+      </c>
+      <c r="W15" s="1">
+        <v>45900</v>
+      </c>
+      <c r="X15" s="1">
+        <v>45907</v>
       </c>
     </row>
     <row r="16" spans="1:24">
-      <c r="A16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" t="s">
-        <v>64</v>
+      <c r="A16" s="1">
+        <v>45840</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="E16" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="F16">
         <v>27.4</v>
@@ -2300,69 +2067,66 @@
         <v>79.40000000000001</v>
       </c>
       <c r="H16" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I16" t="s">
-        <v>160</v>
+        <v>119</v>
       </c>
       <c r="J16" t="s">
+        <v>121</v>
+      </c>
+      <c r="K16" t="s">
+        <v>130</v>
+      </c>
+      <c r="L16" t="s">
+        <v>146</v>
+      </c>
+      <c r="M16" t="s">
+        <v>148</v>
+      </c>
+      <c r="N16" t="s">
+        <v>155</v>
+      </c>
+      <c r="O16" t="s">
+        <v>156</v>
+      </c>
+      <c r="P16" t="s">
         <v>162</v>
       </c>
-      <c r="K16" t="s">
-        <v>171</v>
-      </c>
-      <c r="L16" t="s">
-        <v>187</v>
-      </c>
-      <c r="M16" t="s">
-        <v>189</v>
-      </c>
-      <c r="N16" t="s">
-        <v>196</v>
-      </c>
-      <c r="O16" t="s">
-        <v>197</v>
-      </c>
-      <c r="P16" t="s">
-        <v>203</v>
-      </c>
       <c r="Q16" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="R16" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S16" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="T16">
         <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>232</v>
-      </c>
-      <c r="W16" t="s">
-        <v>266</v>
-      </c>
-      <c r="X16" t="s">
-        <v>283</v>
+        <v>191</v>
+      </c>
+      <c r="W16" s="1">
+        <v>45943</v>
+      </c>
+      <c r="X16" s="1">
+        <v>45946</v>
       </c>
     </row>
     <row r="17" spans="1:24">
-      <c r="A17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" t="s">
-        <v>64</v>
+      <c r="A17" s="1">
+        <v>45834</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="E17" t="s">
-        <v>125</v>
+        <v>84</v>
       </c>
       <c r="F17">
         <v>8</v>
@@ -2371,69 +2135,66 @@
         <v>-80.90000000000001</v>
       </c>
       <c r="H17" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I17" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="J17" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K17" t="s">
-        <v>172</v>
+        <v>131</v>
       </c>
       <c r="L17" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="M17" t="s">
-        <v>194</v>
+        <v>153</v>
       </c>
       <c r="N17" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O17" t="s">
-        <v>199</v>
+        <v>158</v>
       </c>
       <c r="P17" t="s">
-        <v>204</v>
+        <v>163</v>
       </c>
       <c r="Q17" t="s">
-        <v>208</v>
+        <v>167</v>
       </c>
       <c r="R17" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S17" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="T17">
         <v>70</v>
       </c>
       <c r="V17" t="s">
-        <v>233</v>
-      </c>
-      <c r="W17" t="s">
-        <v>271</v>
-      </c>
-      <c r="X17" t="s">
-        <v>285</v>
+        <v>192</v>
+      </c>
+      <c r="W17" s="1">
+        <v>45867</v>
+      </c>
+      <c r="X17" s="1">
+        <v>45879</v>
       </c>
     </row>
     <row r="18" spans="1:24">
-      <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" t="s">
-        <v>64</v>
+      <c r="A18" s="1">
+        <v>45814</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="E18" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="F18">
         <v>20.1</v>
@@ -2442,69 +2203,66 @@
         <v>-100</v>
       </c>
       <c r="H18" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I18" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="J18" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K18" t="s">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="L18" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="M18" t="s">
-        <v>188</v>
+        <v>147</v>
       </c>
       <c r="N18" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O18" t="s">
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="P18" t="s">
-        <v>205</v>
+        <v>164</v>
       </c>
       <c r="Q18" t="s">
-        <v>208</v>
+        <v>167</v>
       </c>
       <c r="R18" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S18" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="T18">
         <v>6</v>
       </c>
       <c r="V18" t="s">
-        <v>234</v>
-      </c>
-      <c r="W18" t="s">
-        <v>33</v>
-      </c>
-      <c r="X18" t="s">
-        <v>285</v>
+        <v>193</v>
+      </c>
+      <c r="W18" s="1">
+        <v>45865</v>
+      </c>
+      <c r="X18" s="1">
+        <v>45879</v>
       </c>
     </row>
     <row r="19" spans="1:24">
-      <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" t="s">
-        <v>64</v>
+      <c r="A19" s="1">
+        <v>45811</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="E19" t="s">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="F19">
         <v>-9.4</v>
@@ -2513,69 +2271,66 @@
         <v>147.2</v>
       </c>
       <c r="H19" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I19" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="J19" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K19" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="L19" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="M19" t="s">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="N19" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O19" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="P19" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q19" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="R19" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S19" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="T19">
         <v>1</v>
       </c>
       <c r="V19" t="s">
-        <v>235</v>
-      </c>
-      <c r="W19" t="s">
-        <v>33</v>
-      </c>
-      <c r="X19" t="s">
-        <v>285</v>
+        <v>194</v>
+      </c>
+      <c r="W19" s="1">
+        <v>45865</v>
+      </c>
+      <c r="X19" s="1">
+        <v>45879</v>
       </c>
     </row>
     <row r="20" spans="1:24">
-      <c r="A20" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" t="s">
-        <v>64</v>
+      <c r="A20" s="1">
+        <v>45810</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="F20">
         <v>-7.8</v>
@@ -2584,69 +2339,66 @@
         <v>-41.9</v>
       </c>
       <c r="H20" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I20" t="s">
+        <v>116</v>
+      </c>
+      <c r="J20" t="s">
+        <v>121</v>
+      </c>
+      <c r="K20" t="s">
+        <v>135</v>
+      </c>
+      <c r="L20" t="s">
+        <v>145</v>
+      </c>
+      <c r="M20" t="s">
+        <v>148</v>
+      </c>
+      <c r="N20" t="s">
+        <v>155</v>
+      </c>
+      <c r="O20" t="s">
         <v>157</v>
       </c>
-      <c r="J20" t="s">
-        <v>162</v>
-      </c>
-      <c r="K20" t="s">
+      <c r="P20" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>167</v>
+      </c>
+      <c r="R20" t="s">
+        <v>170</v>
+      </c>
+      <c r="S20" t="s">
         <v>176</v>
-      </c>
-      <c r="L20" t="s">
-        <v>186</v>
-      </c>
-      <c r="M20" t="s">
-        <v>189</v>
-      </c>
-      <c r="N20" t="s">
-        <v>196</v>
-      </c>
-      <c r="O20" t="s">
-        <v>198</v>
-      </c>
-      <c r="P20" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>208</v>
-      </c>
-      <c r="R20" t="s">
-        <v>211</v>
-      </c>
-      <c r="S20" t="s">
-        <v>217</v>
       </c>
       <c r="T20">
         <v>3</v>
       </c>
       <c r="V20" t="s">
-        <v>236</v>
-      </c>
-      <c r="W20" t="s">
-        <v>33</v>
-      </c>
-      <c r="X20" t="s">
-        <v>285</v>
+        <v>195</v>
+      </c>
+      <c r="W20" s="1">
+        <v>45865</v>
+      </c>
+      <c r="X20" s="1">
+        <v>45879</v>
       </c>
     </row>
     <row r="21" spans="1:24">
-      <c r="A21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" t="s">
-        <v>64</v>
+      <c r="A21" s="1">
+        <v>45804</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="E21" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="F21">
         <v>10.3</v>
@@ -2655,69 +2407,66 @@
         <v>-67</v>
       </c>
       <c r="H21" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I21" t="s">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="J21" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K21" t="s">
-        <v>172</v>
+        <v>131</v>
       </c>
       <c r="L21" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="M21" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="N21" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O21" t="s">
-        <v>199</v>
+        <v>158</v>
       </c>
       <c r="P21" t="s">
-        <v>204</v>
+        <v>163</v>
       </c>
       <c r="Q21" t="s">
-        <v>207</v>
+        <v>166</v>
       </c>
       <c r="R21" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S21" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="T21">
         <v>90</v>
       </c>
       <c r="V21" t="s">
-        <v>237</v>
-      </c>
-      <c r="W21" t="s">
-        <v>272</v>
-      </c>
-      <c r="X21" t="s">
-        <v>273</v>
+        <v>196</v>
+      </c>
+      <c r="W21" s="1">
+        <v>45856</v>
+      </c>
+      <c r="X21" s="1">
+        <v>45858</v>
       </c>
     </row>
     <row r="22" spans="1:24">
-      <c r="A22" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" t="s">
-        <v>64</v>
+      <c r="A22" s="1">
+        <v>45804</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="E22" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="F22">
         <v>-5.1</v>
@@ -2726,69 +2475,66 @@
         <v>119.4</v>
       </c>
       <c r="H22" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I22" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="J22" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K22" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="L22" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="M22" t="s">
-        <v>189</v>
+        <v>148</v>
       </c>
       <c r="N22" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O22" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="P22" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q22" t="s">
-        <v>207</v>
+        <v>166</v>
       </c>
       <c r="R22" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S22" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="T22">
         <v>1</v>
       </c>
       <c r="V22" t="s">
-        <v>238</v>
-      </c>
-      <c r="W22" t="s">
-        <v>33</v>
-      </c>
-      <c r="X22" t="s">
-        <v>285</v>
+        <v>197</v>
+      </c>
+      <c r="W22" s="1">
+        <v>45865</v>
+      </c>
+      <c r="X22" s="1">
+        <v>45879</v>
       </c>
     </row>
     <row r="23" spans="1:24">
-      <c r="A23" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" t="s">
-        <v>64</v>
+      <c r="A23" s="1">
+        <v>45804</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="E23" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="F23">
         <v>-5.3</v>
@@ -2797,69 +2543,66 @@
         <v>119.3</v>
       </c>
       <c r="H23" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I23" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="J23" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K23" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="L23" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="M23" t="s">
-        <v>189</v>
+        <v>148</v>
       </c>
       <c r="N23" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O23" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="P23" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q23" t="s">
-        <v>207</v>
+        <v>166</v>
       </c>
       <c r="R23" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S23" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="T23">
         <v>1</v>
       </c>
       <c r="V23" t="s">
-        <v>239</v>
-      </c>
-      <c r="W23" t="s">
-        <v>33</v>
-      </c>
-      <c r="X23" t="s">
-        <v>285</v>
+        <v>198</v>
+      </c>
+      <c r="W23" s="1">
+        <v>45865</v>
+      </c>
+      <c r="X23" s="1">
+        <v>45879</v>
       </c>
     </row>
     <row r="24" spans="1:24">
-      <c r="A24" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" t="s">
-        <v>64</v>
+      <c r="A24" s="1">
+        <v>45800</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="E24" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="F24">
         <v>24.8</v>
@@ -2868,69 +2611,66 @@
         <v>92.7</v>
       </c>
       <c r="H24" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I24" t="s">
+        <v>115</v>
+      </c>
+      <c r="J24" t="s">
+        <v>121</v>
+      </c>
+      <c r="K24" t="s">
+        <v>130</v>
+      </c>
+      <c r="L24" t="s">
+        <v>145</v>
+      </c>
+      <c r="M24" t="s">
+        <v>150</v>
+      </c>
+      <c r="N24" t="s">
+        <v>155</v>
+      </c>
+      <c r="O24" t="s">
         <v>156</v>
       </c>
-      <c r="J24" t="s">
-        <v>162</v>
-      </c>
-      <c r="K24" t="s">
-        <v>171</v>
-      </c>
-      <c r="L24" t="s">
-        <v>186</v>
-      </c>
-      <c r="M24" t="s">
-        <v>191</v>
-      </c>
-      <c r="N24" t="s">
-        <v>196</v>
-      </c>
-      <c r="O24" t="s">
-        <v>197</v>
-      </c>
       <c r="P24" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q24" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="R24" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S24" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="T24">
         <v>1</v>
       </c>
       <c r="V24" t="s">
-        <v>240</v>
-      </c>
-      <c r="W24" t="s">
-        <v>273</v>
-      </c>
-      <c r="X24" t="s">
-        <v>273</v>
+        <v>199</v>
+      </c>
+      <c r="W24" s="1">
+        <v>45858</v>
+      </c>
+      <c r="X24" s="1">
+        <v>45858</v>
       </c>
     </row>
     <row r="25" spans="1:24">
-      <c r="A25" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" t="s">
-        <v>64</v>
+      <c r="A25" s="1">
+        <v>45796</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="D25" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="E25" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="F25">
         <v>-6.8</v>
@@ -2939,69 +2679,66 @@
         <v>39.2</v>
       </c>
       <c r="H25" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I25" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="J25" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K25" t="s">
-        <v>177</v>
+        <v>136</v>
       </c>
       <c r="L25" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="M25" t="s">
-        <v>189</v>
+        <v>148</v>
       </c>
       <c r="N25" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O25" t="s">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="P25" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q25" t="s">
-        <v>208</v>
+        <v>167</v>
       </c>
       <c r="R25" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S25" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="T25">
         <v>2</v>
       </c>
       <c r="V25" t="s">
-        <v>241</v>
-      </c>
-      <c r="W25" t="s">
-        <v>273</v>
-      </c>
-      <c r="X25" t="s">
-        <v>273</v>
+        <v>200</v>
+      </c>
+      <c r="W25" s="1">
+        <v>45858</v>
+      </c>
+      <c r="X25" s="1">
+        <v>45858</v>
       </c>
     </row>
     <row r="26" spans="1:24">
-      <c r="A26" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" t="s">
-        <v>64</v>
+      <c r="A26" s="1">
+        <v>45783</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="F26">
         <v>33.5</v>
@@ -3010,69 +2747,66 @@
         <v>69.59999999999999</v>
       </c>
       <c r="H26" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I26" t="s">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="J26" t="s">
+        <v>121</v>
+      </c>
+      <c r="K26" t="s">
+        <v>123</v>
+      </c>
+      <c r="L26" t="s">
+        <v>146</v>
+      </c>
+      <c r="M26" t="s">
+        <v>150</v>
+      </c>
+      <c r="N26" t="s">
+        <v>155</v>
+      </c>
+      <c r="O26" t="s">
+        <v>157</v>
+      </c>
+      <c r="P26" t="s">
         <v>162</v>
       </c>
-      <c r="K26" t="s">
-        <v>164</v>
-      </c>
-      <c r="L26" t="s">
-        <v>187</v>
-      </c>
-      <c r="M26" t="s">
-        <v>191</v>
-      </c>
-      <c r="N26" t="s">
-        <v>196</v>
-      </c>
-      <c r="O26" t="s">
-        <v>198</v>
-      </c>
-      <c r="P26" t="s">
-        <v>203</v>
-      </c>
       <c r="Q26" t="s">
-        <v>208</v>
+        <v>167</v>
       </c>
       <c r="R26" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S26" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="T26">
         <v>1</v>
       </c>
       <c r="V26" t="s">
-        <v>242</v>
-      </c>
-      <c r="W26" t="s">
-        <v>273</v>
-      </c>
-      <c r="X26" t="s">
-        <v>273</v>
+        <v>201</v>
+      </c>
+      <c r="W26" s="1">
+        <v>45858</v>
+      </c>
+      <c r="X26" s="1">
+        <v>45858</v>
       </c>
     </row>
     <row r="27" spans="1:24">
-      <c r="A27" t="s">
-        <v>47</v>
-      </c>
-      <c r="B27" t="s">
-        <v>64</v>
+      <c r="A27" s="1">
+        <v>45763</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="E27" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="F27">
         <v>42.8</v>
@@ -3081,69 +2815,66 @@
         <v>74.59999999999999</v>
       </c>
       <c r="H27" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I27" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="J27" t="s">
+        <v>121</v>
+      </c>
+      <c r="K27" t="s">
+        <v>137</v>
+      </c>
+      <c r="L27" t="s">
+        <v>146</v>
+      </c>
+      <c r="M27" t="s">
+        <v>150</v>
+      </c>
+      <c r="N27" t="s">
+        <v>155</v>
+      </c>
+      <c r="O27" t="s">
+        <v>156</v>
+      </c>
+      <c r="P27" t="s">
         <v>162</v>
       </c>
-      <c r="K27" t="s">
-        <v>178</v>
-      </c>
-      <c r="L27" t="s">
-        <v>187</v>
-      </c>
-      <c r="M27" t="s">
-        <v>191</v>
-      </c>
-      <c r="N27" t="s">
-        <v>196</v>
-      </c>
-      <c r="O27" t="s">
-        <v>197</v>
-      </c>
-      <c r="P27" t="s">
-        <v>203</v>
-      </c>
       <c r="Q27" t="s">
-        <v>208</v>
+        <v>167</v>
       </c>
       <c r="R27" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S27" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="T27">
         <v>1</v>
       </c>
       <c r="V27" t="s">
-        <v>243</v>
-      </c>
-      <c r="W27" t="s">
-        <v>274</v>
-      </c>
-      <c r="X27" t="s">
-        <v>286</v>
+        <v>202</v>
+      </c>
+      <c r="W27" s="1">
+        <v>45822</v>
+      </c>
+      <c r="X27" s="1">
+        <v>45839</v>
       </c>
     </row>
     <row r="28" spans="1:24">
-      <c r="A28" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" t="s">
-        <v>64</v>
+      <c r="A28" s="1">
+        <v>45751</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="E28" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="F28">
         <v>-8.1</v>
@@ -3152,69 +2883,66 @@
         <v>111.1</v>
       </c>
       <c r="H28" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I28" t="s">
+        <v>115</v>
+      </c>
+      <c r="J28" t="s">
+        <v>121</v>
+      </c>
+      <c r="K28" t="s">
+        <v>126</v>
+      </c>
+      <c r="L28" t="s">
+        <v>146</v>
+      </c>
+      <c r="M28" t="s">
+        <v>150</v>
+      </c>
+      <c r="N28" t="s">
+        <v>155</v>
+      </c>
+      <c r="O28" t="s">
         <v>156</v>
       </c>
-      <c r="J28" t="s">
-        <v>162</v>
-      </c>
-      <c r="K28" t="s">
-        <v>167</v>
-      </c>
-      <c r="L28" t="s">
-        <v>187</v>
-      </c>
-      <c r="M28" t="s">
-        <v>191</v>
-      </c>
-      <c r="N28" t="s">
-        <v>196</v>
-      </c>
-      <c r="O28" t="s">
-        <v>197</v>
-      </c>
       <c r="P28" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q28" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="R28" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S28" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="T28">
         <v>1</v>
       </c>
       <c r="V28" t="s">
-        <v>244</v>
-      </c>
-      <c r="W28" t="s">
-        <v>274</v>
-      </c>
-      <c r="X28" t="s">
-        <v>286</v>
+        <v>203</v>
+      </c>
+      <c r="W28" s="1">
+        <v>45822</v>
+      </c>
+      <c r="X28" s="1">
+        <v>45839</v>
       </c>
     </row>
     <row r="29" spans="1:24">
-      <c r="A29" t="s">
-        <v>49</v>
-      </c>
-      <c r="B29" t="s">
-        <v>64</v>
+      <c r="A29" s="1">
+        <v>45744</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="D29" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="E29" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="F29">
         <v>49.7</v>
@@ -3223,69 +2951,66 @@
         <v>84.2</v>
       </c>
       <c r="H29" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I29" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="J29" t="s">
+        <v>121</v>
+      </c>
+      <c r="K29" t="s">
+        <v>138</v>
+      </c>
+      <c r="L29" t="s">
+        <v>146</v>
+      </c>
+      <c r="M29" t="s">
+        <v>150</v>
+      </c>
+      <c r="N29" t="s">
+        <v>155</v>
+      </c>
+      <c r="O29" t="s">
+        <v>156</v>
+      </c>
+      <c r="P29" t="s">
         <v>162</v>
       </c>
-      <c r="K29" t="s">
-        <v>179</v>
-      </c>
-      <c r="L29" t="s">
-        <v>187</v>
-      </c>
-      <c r="M29" t="s">
-        <v>191</v>
-      </c>
-      <c r="N29" t="s">
-        <v>196</v>
-      </c>
-      <c r="O29" t="s">
-        <v>197</v>
-      </c>
-      <c r="P29" t="s">
-        <v>203</v>
-      </c>
       <c r="Q29" t="s">
-        <v>208</v>
+        <v>167</v>
       </c>
       <c r="R29" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S29" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="T29">
         <v>1</v>
       </c>
       <c r="V29" t="s">
-        <v>245</v>
-      </c>
-      <c r="W29" t="s">
-        <v>275</v>
-      </c>
-      <c r="X29" t="s">
-        <v>286</v>
+        <v>204</v>
+      </c>
+      <c r="W29" s="1">
+        <v>45809</v>
+      </c>
+      <c r="X29" s="1">
+        <v>45839</v>
       </c>
     </row>
     <row r="30" spans="1:24">
-      <c r="A30" t="s">
+      <c r="A30" s="1">
+        <v>45730</v>
+      </c>
+      <c r="C30" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" t="s">
         <v>50</v>
       </c>
-      <c r="B30" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30" t="s">
-        <v>91</v>
-      </c>
       <c r="E30" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="F30">
         <v>54.7</v>
@@ -3294,69 +3019,66 @@
         <v>55.9</v>
       </c>
       <c r="H30" t="s">
+        <v>109</v>
+      </c>
+      <c r="I30" t="s">
+        <v>115</v>
+      </c>
+      <c r="J30" t="s">
+        <v>121</v>
+      </c>
+      <c r="K30" t="s">
+        <v>131</v>
+      </c>
+      <c r="L30" t="s">
+        <v>146</v>
+      </c>
+      <c r="M30" t="s">
         <v>150</v>
       </c>
-      <c r="I30" t="s">
+      <c r="N30" t="s">
+        <v>155</v>
+      </c>
+      <c r="O30" t="s">
         <v>156</v>
       </c>
-      <c r="J30" t="s">
-        <v>162</v>
-      </c>
-      <c r="K30" t="s">
-        <v>172</v>
-      </c>
-      <c r="L30" t="s">
-        <v>187</v>
-      </c>
-      <c r="M30" t="s">
-        <v>191</v>
-      </c>
-      <c r="N30" t="s">
-        <v>196</v>
-      </c>
-      <c r="O30" t="s">
-        <v>197</v>
-      </c>
       <c r="P30" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q30" t="s">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="R30" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S30" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="T30">
         <v>1</v>
       </c>
       <c r="V30" t="s">
-        <v>246</v>
-      </c>
-      <c r="W30" t="s">
-        <v>42</v>
-      </c>
-      <c r="X30" t="s">
-        <v>286</v>
+        <v>205</v>
+      </c>
+      <c r="W30" s="1">
+        <v>45810</v>
+      </c>
+      <c r="X30" s="1">
+        <v>45839</v>
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" t="s">
-        <v>64</v>
+      <c r="A31" s="1">
+        <v>45726</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="E31" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="F31">
         <v>54.7</v>
@@ -3365,69 +3087,66 @@
         <v>55.9</v>
       </c>
       <c r="H31" t="s">
+        <v>109</v>
+      </c>
+      <c r="I31" t="s">
+        <v>115</v>
+      </c>
+      <c r="J31" t="s">
+        <v>121</v>
+      </c>
+      <c r="K31" t="s">
+        <v>131</v>
+      </c>
+      <c r="L31" t="s">
+        <v>146</v>
+      </c>
+      <c r="M31" t="s">
         <v>150</v>
       </c>
-      <c r="I31" t="s">
+      <c r="N31" t="s">
+        <v>155</v>
+      </c>
+      <c r="O31" t="s">
         <v>156</v>
       </c>
-      <c r="J31" t="s">
-        <v>162</v>
-      </c>
-      <c r="K31" t="s">
-        <v>172</v>
-      </c>
-      <c r="L31" t="s">
-        <v>187</v>
-      </c>
-      <c r="M31" t="s">
-        <v>191</v>
-      </c>
-      <c r="N31" t="s">
-        <v>196</v>
-      </c>
-      <c r="O31" t="s">
-        <v>197</v>
-      </c>
       <c r="P31" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q31" t="s">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="R31" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S31" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="T31">
         <v>1</v>
       </c>
       <c r="V31" t="s">
-        <v>247</v>
-      </c>
-      <c r="W31" t="s">
-        <v>42</v>
-      </c>
-      <c r="X31" t="s">
-        <v>286</v>
+        <v>206</v>
+      </c>
+      <c r="W31" s="1">
+        <v>45810</v>
+      </c>
+      <c r="X31" s="1">
+        <v>45839</v>
       </c>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" t="s">
-        <v>52</v>
-      </c>
-      <c r="B32" t="s">
-        <v>64</v>
+      <c r="A32" s="1">
+        <v>45724</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
+        <v>55</v>
+      </c>
+      <c r="E32" t="s">
         <v>96</v>
-      </c>
-      <c r="E32" t="s">
-        <v>137</v>
       </c>
       <c r="F32">
         <v>18.8</v>
@@ -3436,69 +3155,66 @@
         <v>75.40000000000001</v>
       </c>
       <c r="H32" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I32" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="J32" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K32" t="s">
-        <v>171</v>
+        <v>130</v>
       </c>
       <c r="L32" t="s">
-        <v>187</v>
+        <v>146</v>
       </c>
       <c r="M32" t="s">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="N32" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O32" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="P32" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q32" t="s">
-        <v>208</v>
+        <v>167</v>
       </c>
       <c r="R32" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S32" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="T32">
         <v>1</v>
       </c>
       <c r="V32" t="s">
-        <v>248</v>
-      </c>
-      <c r="W32" t="s">
-        <v>275</v>
-      </c>
-      <c r="X32" t="s">
-        <v>286</v>
+        <v>207</v>
+      </c>
+      <c r="W32" s="1">
+        <v>45809</v>
+      </c>
+      <c r="X32" s="1">
+        <v>45839</v>
       </c>
     </row>
     <row r="33" spans="1:24">
-      <c r="A33" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" t="s">
-        <v>64</v>
+      <c r="A33" s="1">
+        <v>45724</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="D33" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="E33" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="F33">
         <v>54.7</v>
@@ -3507,69 +3223,66 @@
         <v>55.9</v>
       </c>
       <c r="H33" t="s">
+        <v>109</v>
+      </c>
+      <c r="I33" t="s">
+        <v>115</v>
+      </c>
+      <c r="J33" t="s">
+        <v>121</v>
+      </c>
+      <c r="K33" t="s">
+        <v>131</v>
+      </c>
+      <c r="L33" t="s">
+        <v>146</v>
+      </c>
+      <c r="M33" t="s">
         <v>150</v>
       </c>
-      <c r="I33" t="s">
+      <c r="N33" t="s">
+        <v>155</v>
+      </c>
+      <c r="O33" t="s">
         <v>156</v>
       </c>
-      <c r="J33" t="s">
-        <v>162</v>
-      </c>
-      <c r="K33" t="s">
-        <v>172</v>
-      </c>
-      <c r="L33" t="s">
-        <v>187</v>
-      </c>
-      <c r="M33" t="s">
-        <v>191</v>
-      </c>
-      <c r="N33" t="s">
-        <v>196</v>
-      </c>
-      <c r="O33" t="s">
-        <v>197</v>
-      </c>
       <c r="P33" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q33" t="s">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="R33" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S33" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="T33">
         <v>1</v>
       </c>
       <c r="V33" t="s">
-        <v>249</v>
-      </c>
-      <c r="W33" t="s">
-        <v>42</v>
-      </c>
-      <c r="X33" t="s">
-        <v>286</v>
+        <v>208</v>
+      </c>
+      <c r="W33" s="1">
+        <v>45810</v>
+      </c>
+      <c r="X33" s="1">
+        <v>45839</v>
       </c>
     </row>
     <row r="34" spans="1:24">
-      <c r="A34" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" t="s">
-        <v>64</v>
+      <c r="A34" s="1">
+        <v>45718</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="D34" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="E34" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="F34">
         <v>8.300000000000001</v>
@@ -3578,69 +3291,66 @@
         <v>39</v>
       </c>
       <c r="H34" t="s">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="I34" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="J34" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K34" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="L34" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="M34" t="s">
-        <v>189</v>
+        <v>148</v>
       </c>
       <c r="N34" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O34" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="P34" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q34" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="R34" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S34" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="T34">
         <v>2</v>
       </c>
       <c r="V34" t="s">
-        <v>250</v>
-      </c>
-      <c r="W34" t="s">
-        <v>43</v>
-      </c>
-      <c r="X34" t="s">
-        <v>286</v>
+        <v>209</v>
+      </c>
+      <c r="W34" s="1">
+        <v>45804</v>
+      </c>
+      <c r="X34" s="1">
+        <v>45839</v>
       </c>
     </row>
     <row r="35" spans="1:24">
-      <c r="A35" t="s">
-        <v>53</v>
-      </c>
-      <c r="B35" t="s">
-        <v>64</v>
+      <c r="A35" s="1">
+        <v>45718</v>
       </c>
       <c r="C35" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D35" t="s">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="E35" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="F35">
         <v>-23.6</v>
@@ -3649,68 +3359,62 @@
         <v>-46.5</v>
       </c>
       <c r="H35" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I35" t="s">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="J35" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K35" t="s">
-        <v>176</v>
+        <v>135</v>
       </c>
       <c r="L35" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="M35" t="s">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="N35" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O35" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="P35" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q35" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="R35" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S35" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="T35">
         <v>1</v>
       </c>
       <c r="V35" t="s">
-        <v>251</v>
-      </c>
-      <c r="W35" t="s">
+        <v>210</v>
+      </c>
+      <c r="W35" s="1">
+        <v>45810</v>
+      </c>
+      <c r="X35" s="1">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24">
+      <c r="A36" s="1">
+        <v>45708</v>
+      </c>
+      <c r="C36" t="s">
         <v>42</v>
       </c>
-      <c r="X35" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="36" spans="1:24">
-      <c r="A36" t="s">
-        <v>54</v>
-      </c>
-      <c r="B36" t="s">
-        <v>64</v>
-      </c>
-      <c r="C36" t="s">
-        <v>83</v>
-      </c>
       <c r="D36" t="s">
-        <v>105</v>
-      </c>
-      <c r="E36" t="s">
         <v>64</v>
       </c>
       <c r="F36">
@@ -3720,69 +3424,66 @@
         <v>69.2</v>
       </c>
       <c r="H36" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I36" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="J36" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K36" t="s">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="L36" t="s">
-        <v>187</v>
+        <v>146</v>
       </c>
       <c r="M36" t="s">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="N36" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O36" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="P36" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q36" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="R36" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S36" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="T36">
         <v>1</v>
       </c>
       <c r="V36" t="s">
-        <v>252</v>
-      </c>
-      <c r="W36" t="s">
-        <v>276</v>
-      </c>
-      <c r="X36" t="s">
-        <v>286</v>
+        <v>211</v>
+      </c>
+      <c r="W36" s="1">
+        <v>45795</v>
+      </c>
+      <c r="X36" s="1">
+        <v>45839</v>
       </c>
     </row>
     <row r="37" spans="1:24">
-      <c r="A37" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" t="s">
-        <v>64</v>
+      <c r="A37" s="1">
+        <v>45707</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="D37" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="E37" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="F37">
         <v>11.5</v>
@@ -3791,69 +3492,66 @@
         <v>37.3</v>
       </c>
       <c r="H37" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I37" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="J37" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K37" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="L37" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="M37" t="s">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="N37" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O37" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="P37" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q37" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="R37" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S37" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="T37">
         <v>1</v>
       </c>
       <c r="V37" t="s">
-        <v>253</v>
-      </c>
-      <c r="W37" t="s">
-        <v>276</v>
-      </c>
-      <c r="X37" t="s">
-        <v>286</v>
+        <v>212</v>
+      </c>
+      <c r="W37" s="1">
+        <v>45795</v>
+      </c>
+      <c r="X37" s="1">
+        <v>45839</v>
       </c>
     </row>
     <row r="38" spans="1:24">
-      <c r="A38" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" t="s">
-        <v>64</v>
+      <c r="A38" s="1">
+        <v>45706</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="D38" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="E38" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="F38">
         <v>9.1</v>
@@ -3862,69 +3560,66 @@
         <v>80.2</v>
       </c>
       <c r="H38" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I38" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="J38" t="s">
+        <v>121</v>
+      </c>
+      <c r="K38" t="s">
+        <v>141</v>
+      </c>
+      <c r="L38" t="s">
+        <v>146</v>
+      </c>
+      <c r="M38" t="s">
+        <v>154</v>
+      </c>
+      <c r="N38" t="s">
+        <v>155</v>
+      </c>
+      <c r="O38" t="s">
+        <v>156</v>
+      </c>
+      <c r="P38" t="s">
         <v>162</v>
       </c>
-      <c r="K38" t="s">
-        <v>182</v>
-      </c>
-      <c r="L38" t="s">
-        <v>187</v>
-      </c>
-      <c r="M38" t="s">
-        <v>195</v>
-      </c>
-      <c r="N38" t="s">
-        <v>196</v>
-      </c>
-      <c r="O38" t="s">
-        <v>197</v>
-      </c>
-      <c r="P38" t="s">
-        <v>203</v>
-      </c>
       <c r="Q38" t="s">
-        <v>206</v>
+        <v>165</v>
       </c>
       <c r="R38" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S38" t="s">
-        <v>213</v>
+        <v>172</v>
       </c>
       <c r="T38">
         <v>2</v>
       </c>
       <c r="V38" t="s">
-        <v>254</v>
-      </c>
-      <c r="W38" t="s">
-        <v>277</v>
-      </c>
-      <c r="X38" t="s">
-        <v>286</v>
+        <v>213</v>
+      </c>
+      <c r="W38" s="1">
+        <v>45753</v>
+      </c>
+      <c r="X38" s="1">
+        <v>45839</v>
       </c>
     </row>
     <row r="39" spans="1:24">
-      <c r="A39" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" t="s">
-        <v>64</v>
+      <c r="A39" s="1">
+        <v>45704</v>
       </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="E39" t="s">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="F39">
         <v>9.4</v>
@@ -3933,69 +3628,66 @@
         <v>18.8</v>
       </c>
       <c r="H39" t="s">
-        <v>152</v>
+        <v>111</v>
       </c>
       <c r="I39" t="s">
+        <v>115</v>
+      </c>
+      <c r="J39" t="s">
+        <v>121</v>
+      </c>
+      <c r="K39" t="s">
+        <v>142</v>
+      </c>
+      <c r="L39" t="s">
+        <v>145</v>
+      </c>
+      <c r="M39" t="s">
+        <v>150</v>
+      </c>
+      <c r="N39" t="s">
+        <v>155</v>
+      </c>
+      <c r="O39" t="s">
         <v>156</v>
       </c>
-      <c r="J39" t="s">
+      <c r="P39" t="s">
         <v>162</v>
       </c>
-      <c r="K39" t="s">
-        <v>183</v>
-      </c>
-      <c r="L39" t="s">
-        <v>186</v>
-      </c>
-      <c r="M39" t="s">
-        <v>191</v>
-      </c>
-      <c r="N39" t="s">
-        <v>196</v>
-      </c>
-      <c r="O39" t="s">
-        <v>197</v>
-      </c>
-      <c r="P39" t="s">
-        <v>203</v>
-      </c>
       <c r="Q39" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="R39" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S39" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="T39">
         <v>1</v>
       </c>
       <c r="V39" t="s">
-        <v>255</v>
-      </c>
-      <c r="W39" t="s">
-        <v>278</v>
-      </c>
-      <c r="X39" t="s">
-        <v>286</v>
+        <v>214</v>
+      </c>
+      <c r="W39" s="1">
+        <v>45741</v>
+      </c>
+      <c r="X39" s="1">
+        <v>45839</v>
       </c>
     </row>
     <row r="40" spans="1:24">
-      <c r="A40" t="s">
-        <v>57</v>
-      </c>
-      <c r="B40" t="s">
-        <v>64</v>
+      <c r="A40" s="1">
+        <v>45704</v>
       </c>
       <c r="C40" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="D40" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="E40" t="s">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="F40">
         <v>34.1</v>
@@ -4004,69 +3696,66 @@
         <v>62.2</v>
       </c>
       <c r="H40" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I40" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="J40" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K40" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="L40" t="s">
-        <v>187</v>
+        <v>146</v>
       </c>
       <c r="M40" t="s">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="N40" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O40" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="P40" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q40" t="s">
-        <v>208</v>
+        <v>167</v>
       </c>
       <c r="R40" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S40" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="T40">
         <v>1</v>
       </c>
       <c r="V40" t="s">
-        <v>256</v>
-      </c>
-      <c r="W40" t="s">
-        <v>279</v>
-      </c>
-      <c r="X40" t="s">
-        <v>286</v>
+        <v>215</v>
+      </c>
+      <c r="W40" s="1">
+        <v>45746</v>
+      </c>
+      <c r="X40" s="1">
+        <v>45839</v>
       </c>
     </row>
     <row r="41" spans="1:24">
-      <c r="A41" t="s">
-        <v>58</v>
-      </c>
-      <c r="B41" t="s">
-        <v>64</v>
+      <c r="A41" s="1">
+        <v>45694</v>
       </c>
       <c r="C41" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="D41" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="E41" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="F41">
         <v>42.8</v>
@@ -4075,69 +3764,66 @@
         <v>74.59999999999999</v>
       </c>
       <c r="H41" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I41" t="s">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="J41" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K41" t="s">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="L41" t="s">
-        <v>187</v>
+        <v>146</v>
       </c>
       <c r="M41" t="s">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="N41" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O41" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="P41" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q41" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="R41" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S41" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="T41">
         <v>1</v>
       </c>
       <c r="V41" t="s">
-        <v>257</v>
-      </c>
-      <c r="W41" t="s">
-        <v>279</v>
-      </c>
-      <c r="X41" t="s">
-        <v>286</v>
+        <v>216</v>
+      </c>
+      <c r="W41" s="1">
+        <v>45746</v>
+      </c>
+      <c r="X41" s="1">
+        <v>45839</v>
       </c>
     </row>
     <row r="42" spans="1:24">
-      <c r="A42" t="s">
+      <c r="A42" s="1">
+        <v>45694</v>
+      </c>
+      <c r="C42" t="s">
+        <v>34</v>
+      </c>
+      <c r="D42" t="s">
         <v>58</v>
       </c>
-      <c r="B42" t="s">
-        <v>64</v>
-      </c>
-      <c r="C42" t="s">
-        <v>75</v>
-      </c>
-      <c r="D42" t="s">
-        <v>99</v>
-      </c>
       <c r="E42" t="s">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="F42">
         <v>17</v>
@@ -4146,69 +3832,66 @@
         <v>-96.59999999999999</v>
       </c>
       <c r="H42" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I42" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="J42" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K42" t="s">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="L42" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="M42" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="N42" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O42" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="P42" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q42" t="s">
-        <v>207</v>
+        <v>166</v>
       </c>
       <c r="R42" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S42" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="T42">
         <v>1</v>
       </c>
       <c r="V42" t="s">
-        <v>258</v>
-      </c>
-      <c r="W42" t="s">
-        <v>279</v>
-      </c>
-      <c r="X42" t="s">
-        <v>286</v>
+        <v>217</v>
+      </c>
+      <c r="W42" s="1">
+        <v>45746</v>
+      </c>
+      <c r="X42" s="1">
+        <v>45839</v>
       </c>
     </row>
     <row r="43" spans="1:24">
-      <c r="A43" t="s">
-        <v>59</v>
-      </c>
-      <c r="B43" t="s">
-        <v>64</v>
+      <c r="A43" s="1">
+        <v>45687</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="D43" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="F43">
         <v>24.4</v>
@@ -4217,69 +3900,66 @@
         <v>95.40000000000001</v>
       </c>
       <c r="H43" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I43" t="s">
+        <v>115</v>
+      </c>
+      <c r="J43" t="s">
+        <v>121</v>
+      </c>
+      <c r="K43" t="s">
+        <v>131</v>
+      </c>
+      <c r="L43" t="s">
+        <v>146</v>
+      </c>
+      <c r="M43" t="s">
+        <v>150</v>
+      </c>
+      <c r="N43" t="s">
+        <v>155</v>
+      </c>
+      <c r="O43" t="s">
         <v>156</v>
       </c>
-      <c r="J43" t="s">
-        <v>162</v>
-      </c>
-      <c r="K43" t="s">
+      <c r="P43" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>165</v>
+      </c>
+      <c r="R43" t="s">
+        <v>170</v>
+      </c>
+      <c r="S43" t="s">
         <v>172</v>
-      </c>
-      <c r="L43" t="s">
-        <v>187</v>
-      </c>
-      <c r="M43" t="s">
-        <v>191</v>
-      </c>
-      <c r="N43" t="s">
-        <v>196</v>
-      </c>
-      <c r="O43" t="s">
-        <v>197</v>
-      </c>
-      <c r="P43" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>206</v>
-      </c>
-      <c r="R43" t="s">
-        <v>211</v>
-      </c>
-      <c r="S43" t="s">
-        <v>213</v>
       </c>
       <c r="T43">
         <v>1</v>
       </c>
       <c r="V43" t="s">
-        <v>259</v>
-      </c>
-      <c r="W43" t="s">
-        <v>280</v>
-      </c>
-      <c r="X43" t="s">
-        <v>286</v>
+        <v>218</v>
+      </c>
+      <c r="W43" s="1">
+        <v>45727</v>
+      </c>
+      <c r="X43" s="1">
+        <v>45839</v>
       </c>
     </row>
     <row r="44" spans="1:24">
-      <c r="A44" t="s">
-        <v>60</v>
-      </c>
-      <c r="B44" t="s">
-        <v>64</v>
+      <c r="A44" s="1">
+        <v>45677</v>
       </c>
       <c r="C44" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="D44" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="E44" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="F44">
         <v>55.6</v>
@@ -4288,69 +3968,66 @@
         <v>37.6</v>
       </c>
       <c r="H44" t="s">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="I44" t="s">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="J44" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="K44" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="L44" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="M44" t="s">
-        <v>193</v>
+        <v>152</v>
       </c>
       <c r="N44" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="O44" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="P44" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q44" t="s">
-        <v>208</v>
+        <v>167</v>
       </c>
       <c r="R44" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S44" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="T44">
         <v>1</v>
       </c>
       <c r="V44" t="s">
-        <v>260</v>
-      </c>
-      <c r="W44" t="s">
-        <v>51</v>
-      </c>
-      <c r="X44" t="s">
-        <v>286</v>
+        <v>219</v>
+      </c>
+      <c r="W44" s="1">
+        <v>45726</v>
+      </c>
+      <c r="X44" s="1">
+        <v>45839</v>
       </c>
     </row>
     <row r="45" spans="1:24">
-      <c r="A45" t="s">
-        <v>61</v>
-      </c>
-      <c r="B45" t="s">
-        <v>64</v>
+      <c r="A45" s="1">
+        <v>45672</v>
       </c>
       <c r="C45" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="E45" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="F45">
         <v>12.1</v>
@@ -4359,69 +4036,66 @@
         <v>15.1</v>
       </c>
       <c r="H45" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I45" t="s">
+        <v>115</v>
+      </c>
+      <c r="J45" t="s">
+        <v>121</v>
+      </c>
+      <c r="K45" t="s">
+        <v>142</v>
+      </c>
+      <c r="L45" t="s">
+        <v>146</v>
+      </c>
+      <c r="M45" t="s">
+        <v>150</v>
+      </c>
+      <c r="N45" t="s">
+        <v>155</v>
+      </c>
+      <c r="O45" t="s">
         <v>156</v>
       </c>
-      <c r="J45" t="s">
-        <v>162</v>
-      </c>
-      <c r="K45" t="s">
-        <v>183</v>
-      </c>
-      <c r="L45" t="s">
-        <v>187</v>
-      </c>
-      <c r="M45" t="s">
-        <v>191</v>
-      </c>
-      <c r="N45" t="s">
-        <v>196</v>
-      </c>
-      <c r="O45" t="s">
-        <v>197</v>
-      </c>
       <c r="P45" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q45" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="R45" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S45" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="T45">
         <v>1</v>
       </c>
       <c r="V45" t="s">
-        <v>261</v>
-      </c>
-      <c r="W45" t="s">
-        <v>281</v>
-      </c>
-      <c r="X45" t="s">
-        <v>286</v>
+        <v>220</v>
+      </c>
+      <c r="W45" s="1">
+        <v>45725</v>
+      </c>
+      <c r="X45" s="1">
+        <v>45839</v>
       </c>
     </row>
     <row r="46" spans="1:24">
-      <c r="A46" t="s">
-        <v>62</v>
-      </c>
-      <c r="B46" t="s">
-        <v>64</v>
+      <c r="A46" s="1">
+        <v>45671</v>
       </c>
       <c r="C46" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="D46" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="E46" t="s">
-        <v>148</v>
+        <v>107</v>
       </c>
       <c r="F46">
         <v>-33.9</v>
@@ -4430,69 +4104,66 @@
         <v>18.4</v>
       </c>
       <c r="H46" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I46" t="s">
+        <v>115</v>
+      </c>
+      <c r="J46" t="s">
+        <v>121</v>
+      </c>
+      <c r="K46" t="s">
+        <v>143</v>
+      </c>
+      <c r="L46" t="s">
+        <v>146</v>
+      </c>
+      <c r="M46" t="s">
+        <v>150</v>
+      </c>
+      <c r="N46" t="s">
+        <v>155</v>
+      </c>
+      <c r="O46" t="s">
         <v>156</v>
       </c>
-      <c r="J46" t="s">
-        <v>162</v>
-      </c>
-      <c r="K46" t="s">
-        <v>184</v>
-      </c>
-      <c r="L46" t="s">
-        <v>187</v>
-      </c>
-      <c r="M46" t="s">
-        <v>191</v>
-      </c>
-      <c r="N46" t="s">
-        <v>196</v>
-      </c>
-      <c r="O46" t="s">
-        <v>197</v>
-      </c>
       <c r="P46" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="Q46" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="R46" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S46" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="T46">
         <v>1</v>
       </c>
       <c r="V46" t="s">
-        <v>262</v>
-      </c>
-      <c r="W46" t="s">
-        <v>51</v>
-      </c>
-      <c r="X46" t="s">
-        <v>286</v>
+        <v>221</v>
+      </c>
+      <c r="W46" s="1">
+        <v>45726</v>
+      </c>
+      <c r="X46" s="1">
+        <v>45839</v>
       </c>
     </row>
     <row r="47" spans="1:24">
-      <c r="A47" t="s">
-        <v>63</v>
-      </c>
-      <c r="B47" t="s">
-        <v>64</v>
+      <c r="A47" s="1">
+        <v>45669</v>
       </c>
       <c r="C47" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="D47" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="E47" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="F47">
         <v>-8.9</v>
@@ -4501,52 +4172,52 @@
         <v>30.7</v>
       </c>
       <c r="H47" t="s">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="I47" t="s">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="J47" t="s">
+        <v>121</v>
+      </c>
+      <c r="K47" t="s">
+        <v>144</v>
+      </c>
+      <c r="L47" t="s">
+        <v>145</v>
+      </c>
+      <c r="M47" t="s">
+        <v>148</v>
+      </c>
+      <c r="N47" t="s">
+        <v>155</v>
+      </c>
+      <c r="O47" t="s">
+        <v>156</v>
+      </c>
+      <c r="P47" t="s">
         <v>162</v>
       </c>
-      <c r="K47" t="s">
-        <v>185</v>
-      </c>
-      <c r="L47" t="s">
-        <v>186</v>
-      </c>
-      <c r="M47" t="s">
-        <v>189</v>
-      </c>
-      <c r="N47" t="s">
-        <v>196</v>
-      </c>
-      <c r="O47" t="s">
-        <v>197</v>
-      </c>
-      <c r="P47" t="s">
-        <v>203</v>
-      </c>
       <c r="Q47" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="R47" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="S47" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="T47">
         <v>1</v>
       </c>
       <c r="V47" t="s">
-        <v>263</v>
-      </c>
-      <c r="W47" t="s">
-        <v>51</v>
-      </c>
-      <c r="X47" t="s">
-        <v>286</v>
+        <v>222</v>
+      </c>
+      <c r="W47" s="1">
+        <v>45726</v>
+      </c>
+      <c r="X47" s="1">
+        <v>45839</v>
       </c>
     </row>
   </sheetData>

--- a/tests/fixtures/2025 Political-Related Sexual Violence Incident Data.xlsx
+++ b/tests/fixtures/2025 Political-Related Sexual Violence Incident Data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="220">
   <si>
     <t>Date</t>
   </si>
@@ -340,16 +340,7 @@
     <t>Western Cape</t>
   </si>
   <si>
-    <t xml:space="preserve">(5) Linear Feature e.g. Along Road/River </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3) District, Communicipality or Commune </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2) 25 km Precision </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4) Province, State, Governorate </t>
+    <t>censored</t>
   </si>
   <si>
     <t>Whilst Travelling</t>
@@ -1108,53 +1099,47 @@
       <c r="E2" t="s">
         <v>70</v>
       </c>
-      <c r="F2">
-        <v>36.8</v>
-      </c>
-      <c r="G2">
-        <v>71.3</v>
-      </c>
       <c r="H2" t="s">
         <v>108</v>
       </c>
       <c r="I2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="L2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="N2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="R2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="V2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="W2" s="1">
         <v>45957</v>
@@ -1176,53 +1161,47 @@
       <c r="E3" t="s">
         <v>71</v>
       </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>6.8</v>
-      </c>
       <c r="H3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K3" t="s">
         <v>121</v>
       </c>
-      <c r="K3" t="s">
-        <v>124</v>
-      </c>
       <c r="L3" t="s">
+        <v>142</v>
+      </c>
+      <c r="M3" t="s">
         <v>145</v>
       </c>
-      <c r="M3" t="s">
-        <v>148</v>
-      </c>
       <c r="N3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="R3" t="s">
+        <v>167</v>
+      </c>
+      <c r="S3" t="s">
         <v>170</v>
-      </c>
-      <c r="S3" t="s">
-        <v>173</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="W3" s="1">
         <v>45942</v>
@@ -1244,53 +1223,47 @@
       <c r="E4" t="s">
         <v>72</v>
       </c>
-      <c r="F4">
-        <v>43.9</v>
-      </c>
-      <c r="G4">
-        <v>41.1</v>
-      </c>
       <c r="H4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="L4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="N4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="T4">
         <v>1</v>
       </c>
       <c r="V4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="W4" s="1">
         <v>45943</v>
@@ -1312,53 +1285,47 @@
       <c r="E5" t="s">
         <v>73</v>
       </c>
-      <c r="F5">
-        <v>-3.3</v>
-      </c>
-      <c r="G5">
-        <v>120.3</v>
-      </c>
       <c r="H5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q5" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="T5">
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="W5" s="1">
         <v>45943</v>
@@ -1380,53 +1347,47 @@
       <c r="E6" t="s">
         <v>74</v>
       </c>
-      <c r="F6">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="G6">
-        <v>-83.09999999999999</v>
-      </c>
       <c r="H6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="L6" t="s">
+        <v>142</v>
+      </c>
+      <c r="M6" t="s">
         <v>145</v>
       </c>
-      <c r="M6" t="s">
-        <v>148</v>
-      </c>
       <c r="N6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="T6">
         <v>1</v>
       </c>
       <c r="V6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="W6" s="1">
         <v>45936</v>
@@ -1448,53 +1409,47 @@
       <c r="E7" t="s">
         <v>75</v>
       </c>
-      <c r="F7">
-        <v>-2.4</v>
-      </c>
-      <c r="G7">
-        <v>25.9</v>
-      </c>
       <c r="H7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="L7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="R7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S7" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="T7">
         <v>1</v>
       </c>
       <c r="V7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="W7" s="1">
         <v>45940</v>
@@ -1516,53 +1471,47 @@
       <c r="E8" t="s">
         <v>76</v>
       </c>
-      <c r="F8">
-        <v>-3</v>
-      </c>
-      <c r="G8">
-        <v>30.1</v>
-      </c>
       <c r="H8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I8" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J8" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="L8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M8" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P8" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q8" t="s">
+        <v>165</v>
+      </c>
+      <c r="R8" t="s">
         <v>168</v>
       </c>
-      <c r="R8" t="s">
-        <v>171</v>
-      </c>
       <c r="S8" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="T8">
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="W8" s="1">
         <v>45935</v>
@@ -1584,53 +1533,47 @@
       <c r="E9" t="s">
         <v>77</v>
       </c>
-      <c r="F9">
-        <v>-4.4</v>
-      </c>
-      <c r="G9">
-        <v>15.2</v>
-      </c>
       <c r="H9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="L9" t="s">
+        <v>142</v>
+      </c>
+      <c r="M9" t="s">
         <v>145</v>
       </c>
-      <c r="M9" t="s">
-        <v>148</v>
-      </c>
       <c r="N9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="R9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="T9">
         <v>1</v>
       </c>
       <c r="V9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="W9" s="1">
         <v>45940</v>
@@ -1652,53 +1595,47 @@
       <c r="E10" t="s">
         <v>78</v>
       </c>
-      <c r="F10">
-        <v>30.1</v>
-      </c>
-      <c r="G10">
-        <v>76.7</v>
-      </c>
       <c r="H10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J10" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L10" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="N10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O10" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q10" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S10" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="T10">
         <v>1</v>
       </c>
       <c r="V10" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="W10" s="1">
         <v>45943</v>
@@ -1720,53 +1657,47 @@
       <c r="E11" t="s">
         <v>79</v>
       </c>
-      <c r="F11">
-        <v>-3.3</v>
-      </c>
-      <c r="G11">
-        <v>-60.6</v>
-      </c>
       <c r="H11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="R11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S11" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="T11">
         <v>1</v>
       </c>
       <c r="V11" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="W11" s="1">
         <v>45935</v>
@@ -1788,53 +1719,47 @@
       <c r="E12" t="s">
         <v>80</v>
       </c>
-      <c r="F12">
-        <v>29.1</v>
-      </c>
-      <c r="G12">
-        <v>77.59999999999999</v>
-      </c>
       <c r="H12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J12" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L12" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M12" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N12" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O12" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P12" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q12" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="R12" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S12" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="T12">
         <v>2</v>
       </c>
       <c r="V12" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="W12" s="1">
         <v>45943</v>
@@ -1856,53 +1781,47 @@
       <c r="E13" t="s">
         <v>81</v>
       </c>
-      <c r="F13">
-        <v>-3.6</v>
-      </c>
-      <c r="G13">
-        <v>29.3</v>
-      </c>
       <c r="H13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I13" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="L13" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N13" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O13" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P13" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q13" t="s">
+        <v>165</v>
+      </c>
+      <c r="R13" t="s">
         <v>168</v>
       </c>
-      <c r="R13" t="s">
-        <v>171</v>
-      </c>
       <c r="S13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="T13">
         <v>1</v>
       </c>
       <c r="V13" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="W13" s="1">
         <v>45935</v>
@@ -1924,53 +1843,47 @@
       <c r="E14" t="s">
         <v>82</v>
       </c>
-      <c r="F14">
-        <v>24.9</v>
-      </c>
-      <c r="G14">
-        <v>79.5</v>
-      </c>
       <c r="H14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I14" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J14" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K14" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M14" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="N14" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O14" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P14" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="Q14" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S14" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="T14">
         <v>4</v>
       </c>
       <c r="V14" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="W14" s="1">
         <v>45943</v>
@@ -1992,53 +1905,47 @@
       <c r="E15" t="s">
         <v>83</v>
       </c>
-      <c r="F15">
-        <v>-3.2</v>
-      </c>
-      <c r="G15">
-        <v>29.7</v>
-      </c>
       <c r="H15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J15" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K15" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L15" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M15" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N15" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O15" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P15" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q15" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="R15" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S15" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="T15">
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="W15" s="1">
         <v>45900</v>
@@ -2060,53 +1967,47 @@
       <c r="E16" t="s">
         <v>80</v>
       </c>
-      <c r="F16">
-        <v>27.4</v>
-      </c>
-      <c r="G16">
-        <v>79.40000000000001</v>
-      </c>
       <c r="H16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I16" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J16" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K16" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L16" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M16" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="N16" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O16" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P16" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q16" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="R16" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S16" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="T16">
         <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="W16" s="1">
         <v>45943</v>
@@ -2128,53 +2029,47 @@
       <c r="E17" t="s">
         <v>84</v>
       </c>
-      <c r="F17">
-        <v>8</v>
-      </c>
-      <c r="G17">
-        <v>-80.90000000000001</v>
-      </c>
       <c r="H17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I17" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J17" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L17" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M17" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="N17" t="s">
+        <v>152</v>
+      </c>
+      <c r="O17" t="s">
         <v>155</v>
       </c>
-      <c r="O17" t="s">
-        <v>158</v>
-      </c>
       <c r="P17" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="Q17" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R17" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S17" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="T17">
         <v>70</v>
       </c>
       <c r="V17" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="W17" s="1">
         <v>45867</v>
@@ -2196,53 +2091,47 @@
       <c r="E18" t="s">
         <v>85</v>
       </c>
-      <c r="F18">
-        <v>20.1</v>
-      </c>
-      <c r="G18">
-        <v>-100</v>
-      </c>
       <c r="H18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I18" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J18" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K18" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L18" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M18" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="N18" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O18" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="P18" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q18" t="s">
         <v>164</v>
       </c>
-      <c r="Q18" t="s">
-        <v>167</v>
-      </c>
       <c r="R18" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S18" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="T18">
         <v>6</v>
       </c>
       <c r="V18" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="W18" s="1">
         <v>45865</v>
@@ -2264,53 +2153,47 @@
       <c r="E19" t="s">
         <v>86</v>
       </c>
-      <c r="F19">
-        <v>-9.4</v>
-      </c>
-      <c r="G19">
-        <v>147.2</v>
-      </c>
       <c r="H19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K19" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L19" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M19" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N19" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O19" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P19" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q19" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="R19" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S19" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="T19">
         <v>1</v>
       </c>
       <c r="V19" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="W19" s="1">
         <v>45865</v>
@@ -2332,53 +2215,47 @@
       <c r="E20" t="s">
         <v>87</v>
       </c>
-      <c r="F20">
-        <v>-7.8</v>
-      </c>
-      <c r="G20">
-        <v>-41.9</v>
-      </c>
       <c r="H20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J20" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K20" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L20" t="s">
+        <v>142</v>
+      </c>
+      <c r="M20" t="s">
         <v>145</v>
       </c>
-      <c r="M20" t="s">
-        <v>148</v>
-      </c>
       <c r="N20" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O20" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P20" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q20" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R20" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S20" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="T20">
         <v>3</v>
       </c>
       <c r="V20" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="W20" s="1">
         <v>45865</v>
@@ -2400,53 +2277,47 @@
       <c r="E21" t="s">
         <v>88</v>
       </c>
-      <c r="F21">
-        <v>10.3</v>
-      </c>
-      <c r="G21">
-        <v>-67</v>
-      </c>
       <c r="H21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J21" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K21" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L21" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M21" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="N21" t="s">
+        <v>152</v>
+      </c>
+      <c r="O21" t="s">
         <v>155</v>
       </c>
-      <c r="O21" t="s">
-        <v>158</v>
-      </c>
       <c r="P21" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q21" t="s">
         <v>163</v>
       </c>
-      <c r="Q21" t="s">
-        <v>166</v>
-      </c>
       <c r="R21" t="s">
+        <v>167</v>
+      </c>
+      <c r="S21" t="s">
         <v>170</v>
-      </c>
-      <c r="S21" t="s">
-        <v>173</v>
       </c>
       <c r="T21">
         <v>90</v>
       </c>
       <c r="V21" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="W21" s="1">
         <v>45856</v>
@@ -2468,53 +2339,47 @@
       <c r="E22" t="s">
         <v>73</v>
       </c>
-      <c r="F22">
-        <v>-5.1</v>
-      </c>
-      <c r="G22">
-        <v>119.4</v>
-      </c>
       <c r="H22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I22" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J22" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K22" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L22" t="s">
+        <v>142</v>
+      </c>
+      <c r="M22" t="s">
         <v>145</v>
       </c>
-      <c r="M22" t="s">
-        <v>148</v>
-      </c>
       <c r="N22" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O22" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P22" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q22" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="R22" t="s">
+        <v>167</v>
+      </c>
+      <c r="S22" t="s">
         <v>170</v>
-      </c>
-      <c r="S22" t="s">
-        <v>173</v>
       </c>
       <c r="T22">
         <v>1</v>
       </c>
       <c r="V22" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="W22" s="1">
         <v>45865</v>
@@ -2536,53 +2401,47 @@
       <c r="E23" t="s">
         <v>73</v>
       </c>
-      <c r="F23">
-        <v>-5.3</v>
-      </c>
-      <c r="G23">
-        <v>119.3</v>
-      </c>
       <c r="H23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I23" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J23" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K23" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L23" t="s">
+        <v>142</v>
+      </c>
+      <c r="M23" t="s">
         <v>145</v>
       </c>
-      <c r="M23" t="s">
-        <v>148</v>
-      </c>
       <c r="N23" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O23" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P23" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q23" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="R23" t="s">
+        <v>167</v>
+      </c>
+      <c r="S23" t="s">
         <v>170</v>
-      </c>
-      <c r="S23" t="s">
-        <v>173</v>
       </c>
       <c r="T23">
         <v>1</v>
       </c>
       <c r="V23" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="W23" s="1">
         <v>45865</v>
@@ -2604,53 +2463,47 @@
       <c r="E24" t="s">
         <v>89</v>
       </c>
-      <c r="F24">
-        <v>24.8</v>
-      </c>
-      <c r="G24">
-        <v>92.7</v>
-      </c>
       <c r="H24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I24" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J24" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K24" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L24" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M24" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N24" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O24" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P24" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q24" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="R24" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S24" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="T24">
         <v>1</v>
       </c>
       <c r="V24" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="W24" s="1">
         <v>45858</v>
@@ -2672,53 +2525,47 @@
       <c r="E25" t="s">
         <v>90</v>
       </c>
-      <c r="F25">
-        <v>-6.8</v>
-      </c>
-      <c r="G25">
-        <v>39.2</v>
-      </c>
       <c r="H25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I25" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J25" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L25" t="s">
+        <v>142</v>
+      </c>
+      <c r="M25" t="s">
         <v>145</v>
       </c>
-      <c r="M25" t="s">
-        <v>148</v>
-      </c>
       <c r="N25" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O25" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="P25" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q25" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R25" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S25" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="T25">
         <v>2</v>
       </c>
       <c r="V25" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="W25" s="1">
         <v>45858</v>
@@ -2740,53 +2587,47 @@
       <c r="E26" t="s">
         <v>91</v>
       </c>
-      <c r="F26">
-        <v>33.5</v>
-      </c>
-      <c r="G26">
-        <v>69.59999999999999</v>
-      </c>
       <c r="H26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I26" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="J26" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K26" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="L26" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M26" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N26" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O26" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P26" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q26" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R26" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S26" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="T26">
         <v>1</v>
       </c>
       <c r="V26" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="W26" s="1">
         <v>45858</v>
@@ -2808,53 +2649,47 @@
       <c r="E27" t="s">
         <v>92</v>
       </c>
-      <c r="F27">
-        <v>42.8</v>
-      </c>
-      <c r="G27">
-        <v>74.59999999999999</v>
-      </c>
       <c r="H27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I27" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J27" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K27" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="L27" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M27" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N27" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O27" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P27" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q27" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R27" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S27" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="T27">
         <v>1</v>
       </c>
       <c r="V27" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="W27" s="1">
         <v>45822</v>
@@ -2876,53 +2711,47 @@
       <c r="E28" t="s">
         <v>93</v>
       </c>
-      <c r="F28">
-        <v>-8.1</v>
-      </c>
-      <c r="G28">
-        <v>111.1</v>
-      </c>
       <c r="H28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I28" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J28" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K28" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L28" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M28" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N28" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O28" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P28" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q28" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="R28" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S28" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="T28">
         <v>1</v>
       </c>
       <c r="V28" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="W28" s="1">
         <v>45822</v>
@@ -2944,53 +2773,47 @@
       <c r="E29" t="s">
         <v>94</v>
       </c>
-      <c r="F29">
-        <v>49.7</v>
-      </c>
-      <c r="G29">
-        <v>84.2</v>
-      </c>
       <c r="H29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I29" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J29" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K29" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="L29" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M29" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N29" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O29" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P29" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R29" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S29" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="T29">
         <v>1</v>
       </c>
       <c r="V29" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="W29" s="1">
         <v>45809</v>
@@ -3012,53 +2835,47 @@
       <c r="E30" t="s">
         <v>95</v>
       </c>
-      <c r="F30">
-        <v>54.7</v>
-      </c>
-      <c r="G30">
-        <v>55.9</v>
-      </c>
       <c r="H30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I30" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J30" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K30" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L30" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M30" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N30" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O30" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P30" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q30" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="R30" t="s">
+        <v>167</v>
+      </c>
+      <c r="S30" t="s">
         <v>170</v>
-      </c>
-      <c r="S30" t="s">
-        <v>173</v>
       </c>
       <c r="T30">
         <v>1</v>
       </c>
       <c r="V30" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="W30" s="1">
         <v>45810</v>
@@ -3080,53 +2897,47 @@
       <c r="E31" t="s">
         <v>95</v>
       </c>
-      <c r="F31">
-        <v>54.7</v>
-      </c>
-      <c r="G31">
-        <v>55.9</v>
-      </c>
       <c r="H31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I31" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J31" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K31" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L31" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M31" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N31" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O31" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P31" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q31" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="R31" t="s">
+        <v>167</v>
+      </c>
+      <c r="S31" t="s">
         <v>170</v>
-      </c>
-      <c r="S31" t="s">
-        <v>173</v>
       </c>
       <c r="T31">
         <v>1</v>
       </c>
       <c r="V31" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="W31" s="1">
         <v>45810</v>
@@ -3148,53 +2959,47 @@
       <c r="E32" t="s">
         <v>96</v>
       </c>
-      <c r="F32">
-        <v>18.8</v>
-      </c>
-      <c r="G32">
-        <v>75.40000000000001</v>
-      </c>
       <c r="H32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I32" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J32" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K32" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L32" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M32" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N32" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O32" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P32" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q32" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R32" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S32" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="T32">
         <v>1</v>
       </c>
       <c r="V32" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="W32" s="1">
         <v>45809</v>
@@ -3216,53 +3021,47 @@
       <c r="E33" t="s">
         <v>95</v>
       </c>
-      <c r="F33">
-        <v>54.7</v>
-      </c>
-      <c r="G33">
-        <v>55.9</v>
-      </c>
       <c r="H33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I33" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J33" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K33" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L33" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M33" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N33" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O33" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P33" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q33" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="R33" t="s">
+        <v>167</v>
+      </c>
+      <c r="S33" t="s">
         <v>170</v>
-      </c>
-      <c r="S33" t="s">
-        <v>173</v>
       </c>
       <c r="T33">
         <v>1</v>
       </c>
       <c r="V33" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="W33" s="1">
         <v>45810</v>
@@ -3284,53 +3083,47 @@
       <c r="E34" t="s">
         <v>97</v>
       </c>
-      <c r="F34">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="G34">
-        <v>39</v>
-      </c>
       <c r="H34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I34" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J34" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K34" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="L34" t="s">
+        <v>142</v>
+      </c>
+      <c r="M34" t="s">
         <v>145</v>
       </c>
-      <c r="M34" t="s">
-        <v>148</v>
-      </c>
       <c r="N34" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O34" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P34" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q34" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="R34" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S34" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="T34">
         <v>2</v>
       </c>
       <c r="V34" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="W34" s="1">
         <v>45804</v>
@@ -3352,53 +3145,47 @@
       <c r="E35" t="s">
         <v>98</v>
       </c>
-      <c r="F35">
-        <v>-23.6</v>
-      </c>
-      <c r="G35">
-        <v>-46.5</v>
-      </c>
       <c r="H35" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I35" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="J35" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K35" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L35" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M35" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N35" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O35" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P35" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q35" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="R35" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S35" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="T35">
         <v>1</v>
       </c>
       <c r="V35" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="W35" s="1">
         <v>45810</v>
@@ -3417,53 +3204,47 @@
       <c r="D36" t="s">
         <v>64</v>
       </c>
-      <c r="F36">
-        <v>41.3</v>
-      </c>
-      <c r="G36">
-        <v>69.2</v>
-      </c>
       <c r="H36" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I36" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J36" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K36" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="L36" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M36" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N36" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O36" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P36" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q36" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="R36" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S36" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="T36">
         <v>1</v>
       </c>
       <c r="V36" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="W36" s="1">
         <v>45795</v>
@@ -3485,53 +3266,47 @@
       <c r="E37" t="s">
         <v>99</v>
       </c>
-      <c r="F37">
-        <v>11.5</v>
-      </c>
-      <c r="G37">
-        <v>37.3</v>
-      </c>
       <c r="H37" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I37" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K37" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="L37" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N37" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O37" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P37" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q37" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="R37" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S37" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="T37">
         <v>1</v>
       </c>
       <c r="V37" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="W37" s="1">
         <v>45795</v>
@@ -3553,53 +3328,47 @@
       <c r="E38" t="s">
         <v>100</v>
       </c>
-      <c r="F38">
-        <v>9.1</v>
-      </c>
-      <c r="G38">
-        <v>80.2</v>
-      </c>
       <c r="H38" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I38" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="J38" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K38" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="L38" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M38" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="N38" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O38" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P38" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q38" t="s">
         <v>162</v>
       </c>
-      <c r="Q38" t="s">
-        <v>165</v>
-      </c>
       <c r="R38" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S38" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="T38">
         <v>2</v>
       </c>
       <c r="V38" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="W38" s="1">
         <v>45753</v>
@@ -3621,53 +3390,47 @@
       <c r="E39" t="s">
         <v>101</v>
       </c>
-      <c r="F39">
-        <v>9.4</v>
-      </c>
-      <c r="G39">
-        <v>18.8</v>
-      </c>
       <c r="H39" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I39" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J39" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K39" t="s">
+        <v>139</v>
+      </c>
+      <c r="L39" t="s">
         <v>142</v>
       </c>
-      <c r="L39" t="s">
-        <v>145</v>
-      </c>
       <c r="M39" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N39" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O39" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P39" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q39" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="R39" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S39" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="T39">
         <v>1</v>
       </c>
       <c r="V39" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="W39" s="1">
         <v>45741</v>
@@ -3689,53 +3452,47 @@
       <c r="E40" t="s">
         <v>102</v>
       </c>
-      <c r="F40">
-        <v>34.1</v>
-      </c>
-      <c r="G40">
-        <v>62.2</v>
-      </c>
       <c r="H40" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I40" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J40" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K40" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="L40" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M40" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N40" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O40" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P40" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q40" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R40" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S40" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="T40">
         <v>1</v>
       </c>
       <c r="V40" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W40" s="1">
         <v>45746</v>
@@ -3757,53 +3514,47 @@
       <c r="E41" t="s">
         <v>92</v>
       </c>
-      <c r="F41">
-        <v>42.8</v>
-      </c>
-      <c r="G41">
-        <v>74.59999999999999</v>
-      </c>
       <c r="H41" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I41" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J41" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K41" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="L41" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M41" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N41" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O41" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P41" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q41" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="R41" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S41" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="T41">
         <v>1</v>
       </c>
       <c r="V41" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="W41" s="1">
         <v>45746</v>
@@ -3825,53 +3576,47 @@
       <c r="E42" t="s">
         <v>103</v>
       </c>
-      <c r="F42">
-        <v>17</v>
-      </c>
-      <c r="G42">
-        <v>-96.59999999999999</v>
-      </c>
       <c r="H42" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I42" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J42" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K42" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L42" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M42" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="N42" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O42" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P42" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q42" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="R42" t="s">
+        <v>167</v>
+      </c>
+      <c r="S42" t="s">
         <v>170</v>
-      </c>
-      <c r="S42" t="s">
-        <v>173</v>
       </c>
       <c r="T42">
         <v>1</v>
       </c>
       <c r="V42" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="W42" s="1">
         <v>45746</v>
@@ -3893,53 +3638,47 @@
       <c r="E43" t="s">
         <v>104</v>
       </c>
-      <c r="F43">
-        <v>24.4</v>
-      </c>
-      <c r="G43">
-        <v>95.40000000000001</v>
-      </c>
       <c r="H43" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I43" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J43" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K43" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L43" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M43" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N43" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O43" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P43" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q43" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="R43" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S43" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="T43">
         <v>1</v>
       </c>
       <c r="V43" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="W43" s="1">
         <v>45727</v>
@@ -3961,53 +3700,47 @@
       <c r="E44" t="s">
         <v>105</v>
       </c>
-      <c r="F44">
-        <v>55.6</v>
-      </c>
-      <c r="G44">
-        <v>37.6</v>
-      </c>
       <c r="H44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I44" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J44" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K44" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="L44" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M44" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="N44" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O44" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P44" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q44" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R44" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S44" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="T44">
         <v>1</v>
       </c>
       <c r="V44" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="W44" s="1">
         <v>45726</v>
@@ -4029,53 +3762,47 @@
       <c r="E45" t="s">
         <v>106</v>
       </c>
-      <c r="F45">
-        <v>12.1</v>
-      </c>
-      <c r="G45">
-        <v>15.1</v>
-      </c>
       <c r="H45" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I45" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J45" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K45" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="L45" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M45" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N45" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O45" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P45" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q45" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="R45" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S45" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="T45">
         <v>1</v>
       </c>
       <c r="V45" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="W45" s="1">
         <v>45725</v>
@@ -4097,53 +3824,47 @@
       <c r="E46" t="s">
         <v>107</v>
       </c>
-      <c r="F46">
-        <v>-33.9</v>
-      </c>
-      <c r="G46">
-        <v>18.4</v>
-      </c>
       <c r="H46" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I46" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J46" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K46" t="s">
+        <v>140</v>
+      </c>
+      <c r="L46" t="s">
         <v>143</v>
       </c>
-      <c r="L46" t="s">
-        <v>146</v>
-      </c>
       <c r="M46" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N46" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O46" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P46" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q46" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="R46" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S46" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="T46">
         <v>1</v>
       </c>
       <c r="V46" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="W46" s="1">
         <v>45726</v>
@@ -4165,53 +3886,47 @@
       <c r="E47" t="s">
         <v>100</v>
       </c>
-      <c r="F47">
-        <v>-8.9</v>
-      </c>
-      <c r="G47">
-        <v>30.7</v>
-      </c>
       <c r="H47" t="s">
+        <v>108</v>
+      </c>
+      <c r="I47" t="s">
         <v>109</v>
       </c>
-      <c r="I47" t="s">
-        <v>112</v>
-      </c>
       <c r="J47" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K47" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L47" t="s">
+        <v>142</v>
+      </c>
+      <c r="M47" t="s">
         <v>145</v>
       </c>
-      <c r="M47" t="s">
-        <v>148</v>
-      </c>
       <c r="N47" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O47" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P47" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q47" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="R47" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S47" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="T47">
         <v>1</v>
       </c>
       <c r="V47" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="W47" s="1">
         <v>45726</v>
